--- a/SRI/Procesamiento/Resultados/DINA_graficos/serie_graficos_dina_2010_2024.xlsx
+++ b/SRI/Procesamiento/Resultados/DINA_graficos/serie_graficos_dina_2010_2024.xlsx
@@ -179,52 +179,52 @@
         <v>2147</v>
       </c>
       <c r="C2" s="1">
-        <v>5.1432202893685384</v>
+        <v>4.1172500315923237</v>
       </c>
       <c r="D2" s="1">
         <v>21462</v>
       </c>
       <c r="E2" s="1">
-        <v>14.11050920652929</v>
+        <v>12.03806243676795</v>
       </c>
       <c r="F2" s="1">
-        <v>214687</v>
+        <v>214615</v>
       </c>
       <c r="G2" s="1">
-        <v>43.620466909372077</v>
+        <v>40.914167995011027</v>
       </c>
       <c r="H2" s="1">
-        <v>858475</v>
+        <v>858462</v>
       </c>
       <c r="I2" s="1">
-        <v>42.633682024761278</v>
+        <v>44.596250924541998</v>
       </c>
       <c r="J2" s="1">
-        <v>1073074</v>
+        <v>1073075</v>
       </c>
       <c r="K2" s="1">
-        <v>13.75413668348091</v>
+        <v>14.489732619114889</v>
       </c>
       <c r="L2" s="1">
-        <v>8.7776303449309197</v>
+        <v>9.2476393463904856</v>
       </c>
       <c r="M2" s="1">
-        <v>751152</v>
+        <v>751153</v>
       </c>
       <c r="N2" s="1">
-        <v>6.6953224849570274</v>
+        <v>7.0542545722433321</v>
       </c>
       <c r="O2" s="1">
-        <v>4.9695038795471192</v>
+        <v>4.4242825508117676</v>
       </c>
       <c r="P2" s="1">
-        <v>41.943128170624718</v>
+        <v>39.355522959361892</v>
       </c>
       <c r="Q2" s="1">
-        <v>9.0618927940663383</v>
+        <v>9.515794552180509</v>
       </c>
       <c r="R2" s="1">
-        <v>4.6285171508789063</v>
+        <v>4.135810375213623</v>
       </c>
     </row>
     <row r="3">
@@ -235,52 +235,52 @@
         <v>2443</v>
       </c>
       <c r="C3" s="1">
-        <v>6.7065839162322298</v>
+        <v>5.331194516162407</v>
       </c>
       <c r="D3" s="1">
         <v>24430</v>
       </c>
       <c r="E3" s="1">
-        <v>15.63404359613606</v>
+        <v>13.24990470834017</v>
       </c>
       <c r="F3" s="1">
         <v>244292</v>
       </c>
       <c r="G3" s="1">
-        <v>44.494300839925231</v>
+        <v>41.573131896183007</v>
       </c>
       <c r="H3" s="1">
         <v>977166</v>
       </c>
       <c r="I3" s="1">
-        <v>41.839106626519609</v>
+        <v>43.937426796957361</v>
       </c>
       <c r="J3" s="1">
         <v>1221457</v>
       </c>
       <c r="K3" s="1">
-        <v>13.66667435386338</v>
+        <v>14.48952504555271</v>
       </c>
       <c r="L3" s="1">
-        <v>8.6844238529479529</v>
+        <v>9.2083479498556162</v>
       </c>
       <c r="M3" s="1">
         <v>855020</v>
       </c>
       <c r="N3" s="1">
-        <v>6.594787781042041</v>
+        <v>6.9929325548415617</v>
       </c>
       <c r="O3" s="1">
-        <v>5.1234602928161621</v>
+        <v>4.5147218704223633</v>
       </c>
       <c r="P3" s="1">
-        <v>42.708640547586747</v>
+        <v>39.931546018720013</v>
       </c>
       <c r="Q3" s="1">
-        <v>8.988841168566065</v>
+        <v>9.4915021421918162</v>
       </c>
       <c r="R3" s="1">
-        <v>4.7512955665588379</v>
+        <v>4.2070837020874023</v>
       </c>
     </row>
     <row r="4">
@@ -291,52 +291,52 @@
         <v>2676</v>
       </c>
       <c r="C4" s="1">
-        <v>6.5391566614600727</v>
+        <v>4.9758195114072263</v>
       </c>
       <c r="D4" s="1">
         <v>26751</v>
       </c>
       <c r="E4" s="1">
-        <v>15.68412800038492</v>
+        <v>13.064085672727931</v>
       </c>
       <c r="F4" s="1">
-        <v>267639</v>
+        <v>267505</v>
       </c>
       <c r="G4" s="1">
-        <v>44.51883696279301</v>
+        <v>41.232006798146763</v>
       </c>
       <c r="H4" s="1">
-        <v>1070717</v>
+        <v>1070017</v>
       </c>
       <c r="I4" s="1">
-        <v>41.584091653344771</v>
+        <v>43.854822851151077</v>
       </c>
       <c r="J4" s="1">
         <v>1337521</v>
       </c>
       <c r="K4" s="1">
-        <v>13.959004329518599</v>
+        <v>14.91326875537475</v>
       </c>
       <c r="L4" s="1">
-        <v>8.8942856985470851</v>
+        <v>9.5035486702739736</v>
       </c>
       <c r="M4" s="1">
         <v>936265</v>
       </c>
       <c r="N4" s="1">
-        <v>6.7635061294378698</v>
+        <v>7.2270467675392709</v>
       </c>
       <c r="O4" s="1">
-        <v>5.0053300857543945</v>
+        <v>4.3385906219482422</v>
       </c>
       <c r="P4" s="1">
-        <v>42.652308801990863</v>
+        <v>39.562349655937311</v>
       </c>
       <c r="Q4" s="1">
-        <v>9.2175542873051519</v>
+        <v>9.7994966354335542</v>
       </c>
       <c r="R4" s="1">
-        <v>4.627291202545166</v>
+        <v>4.0371818542480469</v>
       </c>
     </row>
     <row r="5">
@@ -347,52 +347,52 @@
         <v>2971</v>
       </c>
       <c r="C5" s="1">
-        <v>7.1114686457304757</v>
+        <v>4.6892693448886931</v>
       </c>
       <c r="D5" s="1">
         <v>29709</v>
       </c>
       <c r="E5" s="1">
-        <v>16.27188913416023</v>
+        <v>12.738952217097779</v>
       </c>
       <c r="F5" s="1">
         <v>297083</v>
       </c>
       <c r="G5" s="1">
-        <v>44.995543458304383</v>
+        <v>40.974649679897837</v>
       </c>
       <c r="H5" s="1">
-        <v>1188329</v>
+        <v>1188331</v>
       </c>
       <c r="I5" s="1">
-        <v>40.761749499073368</v>
+        <v>43.602520883001823</v>
       </c>
       <c r="J5" s="1">
-        <v>1485411</v>
+        <v>1485414</v>
       </c>
       <c r="K5" s="1">
-        <v>14.242773336017679</v>
+        <v>15.42296027514521</v>
       </c>
       <c r="L5" s="1">
-        <v>9.1071085993068905</v>
+        <v>9.8630274968766436</v>
       </c>
       <c r="M5" s="1">
-        <v>1039788</v>
+        <v>1039789</v>
       </c>
       <c r="N5" s="1">
-        <v>6.9280625993238729</v>
+        <v>7.5032601073094423</v>
       </c>
       <c r="O5" s="1">
-        <v>4.9407057762145996</v>
+        <v>4.1543684005737305</v>
       </c>
       <c r="P5" s="1">
-        <v>43.154132936434181</v>
+        <v>39.320246882137319</v>
       </c>
       <c r="Q5" s="1">
-        <v>9.4340026142645197</v>
+        <v>10.16072797021517</v>
       </c>
       <c r="R5" s="1">
-        <v>4.5743184089660645</v>
+        <v>3.8698258399963379</v>
       </c>
     </row>
     <row r="6">
@@ -403,52 +403,52 @@
         <v>3225</v>
       </c>
       <c r="C6" s="1">
-        <v>8.1459246039837261</v>
+        <v>6.0649708523053683</v>
       </c>
       <c r="D6" s="1">
-        <v>32250</v>
+        <v>32253</v>
       </c>
       <c r="E6" s="1">
-        <v>17.425576796331441</v>
+        <v>14.20646735919977</v>
       </c>
       <c r="F6" s="1">
-        <v>322494</v>
+        <v>322656</v>
       </c>
       <c r="G6" s="1">
-        <v>46.342613808854921</v>
+        <v>42.00098006736669</v>
       </c>
       <c r="H6" s="1">
-        <v>1289976</v>
+        <v>1290114</v>
       </c>
       <c r="I6" s="1">
-        <v>39.645648778145073</v>
+        <v>42.591649989334677</v>
       </c>
       <c r="J6" s="1">
         <v>1612469</v>
       </c>
       <c r="K6" s="1">
-        <v>14.0118153000722</v>
+        <v>15.425919585710229</v>
       </c>
       <c r="L6" s="1">
-        <v>8.972005120096826</v>
+        <v>9.8797623308840734</v>
       </c>
       <c r="M6" s="1">
-        <v>1128728</v>
+        <v>1128994</v>
       </c>
       <c r="N6" s="1">
-        <v>6.8115628944674711</v>
+        <v>7.5045917059735343</v>
       </c>
       <c r="O6" s="1">
-        <v>5.1652460098266602</v>
+        <v>4.251213550567627</v>
       </c>
       <c r="P6" s="1">
-        <v>44.608065699129121</v>
+        <v>40.384609979881382</v>
       </c>
       <c r="Q6" s="1">
-        <v>9.2839739846185054</v>
+        <v>10.173153579213929</v>
       </c>
       <c r="R6" s="1">
-        <v>4.8048458099365234</v>
+        <v>3.9697237014770508</v>
       </c>
     </row>
     <row r="7">
@@ -459,52 +459,52 @@
         <v>3250</v>
       </c>
       <c r="C7" s="1">
-        <v>6.5895210154517807</v>
+        <v>4.5564921208044869</v>
       </c>
       <c r="D7" s="1">
         <v>32496</v>
       </c>
       <c r="E7" s="1">
-        <v>16.458675114797469</v>
+        <v>13.059790234908011</v>
       </c>
       <c r="F7" s="1">
         <v>324957</v>
       </c>
       <c r="G7" s="1">
-        <v>45.643057385940921</v>
+        <v>41.291065155300991</v>
       </c>
       <c r="H7" s="1">
-        <v>1299825</v>
+        <v>1299830</v>
       </c>
       <c r="I7" s="1">
-        <v>39.918268181938743</v>
+        <v>42.968255368297847</v>
       </c>
       <c r="J7" s="1">
-        <v>1624781</v>
+        <v>1624783</v>
       </c>
       <c r="K7" s="1">
-        <v>14.438733933152299</v>
+        <v>15.74087707740285</v>
       </c>
       <c r="L7" s="1">
-        <v>9.2326715087309985</v>
+        <v>10.066691701625709</v>
       </c>
       <c r="M7" s="1">
-        <v>1137442</v>
+        <v>1137348</v>
       </c>
       <c r="N7" s="1">
-        <v>7.0149666383006126</v>
+        <v>7.6474736929959226</v>
       </c>
       <c r="O7" s="1">
-        <v>4.9436459541320801</v>
+        <v>4.1017513275146484</v>
       </c>
       <c r="P7" s="1">
-        <v>43.929972227835613</v>
+        <v>39.759078880050872</v>
       </c>
       <c r="Q7" s="1">
-        <v>9.5422805878432833</v>
+        <v>10.34725961944525</v>
       </c>
       <c r="R7" s="1">
-        <v>4.6037182807922363</v>
+        <v>3.8424742221832275</v>
       </c>
     </row>
     <row r="8">
@@ -515,52 +515,52 @@
         <v>3195</v>
       </c>
       <c r="C8" s="1">
-        <v>6.9621282743079451</v>
+        <v>4.9307695264503151</v>
       </c>
       <c r="D8" s="1">
         <v>31947</v>
       </c>
       <c r="E8" s="1">
-        <v>16.686443233606969</v>
+        <v>13.370817603702349</v>
       </c>
       <c r="F8" s="1">
         <v>319463</v>
       </c>
       <c r="G8" s="1">
-        <v>45.479918034533988</v>
+        <v>41.446059123778987</v>
       </c>
       <c r="H8" s="1">
-        <v>1277854</v>
+        <v>1277853</v>
       </c>
       <c r="I8" s="1">
-        <v>40.085114603990533</v>
+        <v>42.922251002431842</v>
       </c>
       <c r="J8" s="1">
         <v>1597314</v>
       </c>
       <c r="K8" s="1">
-        <v>14.435082769488041</v>
+        <v>15.63179208864266</v>
       </c>
       <c r="L8" s="1">
-        <v>9.1591889829789395</v>
+        <v>9.9198444695384822</v>
       </c>
       <c r="M8" s="1">
         <v>1118120</v>
       </c>
       <c r="N8" s="1">
-        <v>6.8940951254164968</v>
+        <v>7.4665231286749094</v>
       </c>
       <c r="O8" s="1">
-        <v>4.9654960632324219</v>
+        <v>4.178095817565918</v>
       </c>
       <c r="P8" s="1">
-        <v>43.842602251747501</v>
+        <v>40.04262703971871</v>
       </c>
       <c r="Q8" s="1">
-        <v>9.4486423506634143</v>
+        <v>10.171486256620399</v>
       </c>
       <c r="R8" s="1">
-        <v>4.6400952339172363</v>
+        <v>3.9367527961730957</v>
       </c>
     </row>
     <row r="9">
@@ -571,52 +571,52 @@
         <v>3258</v>
       </c>
       <c r="C9" s="1">
-        <v>6.7911005383172238</v>
+        <v>4.7449261509294951</v>
       </c>
       <c r="D9" s="1">
         <v>32579</v>
       </c>
       <c r="E9" s="1">
-        <v>16.261654794499041</v>
+        <v>12.982047529060599</v>
       </c>
       <c r="F9" s="1">
         <v>325790</v>
       </c>
       <c r="G9" s="1">
-        <v>45.105660632955598</v>
+        <v>40.954316930625133</v>
       </c>
       <c r="H9" s="1">
-        <v>1303920</v>
+        <v>1303161</v>
       </c>
       <c r="I9" s="1">
-        <v>40.342301035747681</v>
+        <v>43.230688518082793</v>
       </c>
       <c r="J9" s="1">
-        <v>1630653</v>
+        <v>1628950</v>
       </c>
       <c r="K9" s="1">
-        <v>14.59683387304878</v>
+        <v>15.81507534125705</v>
       </c>
       <c r="L9" s="1">
-        <v>9.2499326372626225</v>
+        <v>10.044884898934001</v>
       </c>
       <c r="M9" s="1">
-        <v>1140266</v>
+        <v>1140275</v>
       </c>
       <c r="N9" s="1">
-        <v>6.9839597703472798</v>
+        <v>7.5842509865497938</v>
       </c>
       <c r="O9" s="1">
-        <v>4.8763232231140137</v>
+        <v>4.0771317481994629</v>
       </c>
       <c r="P9" s="1">
-        <v>43.420318644414202</v>
+        <v>39.483019845653317</v>
       </c>
       <c r="Q9" s="1">
-        <v>9.5491043897938823</v>
+        <v>10.309799663972861</v>
       </c>
       <c r="R9" s="1">
-        <v>4.5470566749572754</v>
+        <v>3.8296592235565186</v>
       </c>
     </row>
     <row r="10">
@@ -627,52 +627,52 @@
         <v>3314</v>
       </c>
       <c r="C10" s="1">
-        <v>6.7450491568886441</v>
+        <v>4.5624814516639516</v>
       </c>
       <c r="D10" s="1">
         <v>33139</v>
       </c>
       <c r="E10" s="1">
-        <v>16.137903998311011</v>
+        <v>12.80277798836161</v>
       </c>
       <c r="F10" s="1">
-        <v>331384</v>
+        <v>331385</v>
       </c>
       <c r="G10" s="1">
-        <v>44.690424394246037</v>
+        <v>40.567150791443289</v>
       </c>
       <c r="H10" s="1">
-        <v>1325536</v>
+        <v>1325537</v>
       </c>
       <c r="I10" s="1">
-        <v>40.44854005562032</v>
+        <v>43.305699469081112</v>
       </c>
       <c r="J10" s="1">
-        <v>1656919</v>
+        <v>1656921</v>
       </c>
       <c r="K10" s="1">
-        <v>14.86109387868057</v>
+        <v>16.127209425425772</v>
       </c>
       <c r="L10" s="1">
-        <v>9.4481314356595831</v>
+        <v>10.254925083300961</v>
       </c>
       <c r="M10" s="1">
-        <v>1159844</v>
+        <v>1159848</v>
       </c>
       <c r="N10" s="1">
-        <v>7.1444012337111227</v>
+        <v>7.7543851764170251</v>
       </c>
       <c r="O10" s="1">
-        <v>4.7300806045532227</v>
+        <v>3.9558699131011963</v>
       </c>
       <c r="P10" s="1">
-        <v>42.987462895608339</v>
+        <v>39.091525309514168</v>
       </c>
       <c r="Q10" s="1">
-        <v>9.7554045748953815</v>
+        <v>10.52475499775742</v>
       </c>
       <c r="R10" s="1">
-        <v>4.4065279960632324</v>
+        <v>3.7142455577850342</v>
       </c>
     </row>
     <row r="11">
@@ -683,52 +683,52 @@
         <v>3321</v>
       </c>
       <c r="C11" s="1">
-        <v>6.8077363973346374</v>
+        <v>5.0540715804061316</v>
       </c>
       <c r="D11" s="1">
         <v>33205</v>
       </c>
       <c r="E11" s="1">
-        <v>15.77874208956961</v>
+        <v>13.015204158091031</v>
       </c>
       <c r="F11" s="1">
-        <v>332046</v>
+        <v>332081</v>
       </c>
       <c r="G11" s="1">
-        <v>43.01475712701383</v>
+        <v>39.396418806294577</v>
       </c>
       <c r="H11" s="1">
-        <v>1328183</v>
+        <v>1328498</v>
       </c>
       <c r="I11" s="1">
-        <v>41.136459730138</v>
+        <v>43.615440502513018</v>
       </c>
       <c r="J11" s="1">
         <v>1660228</v>
       </c>
       <c r="K11" s="1">
-        <v>15.848857888769061</v>
+        <v>17.008574990063401</v>
       </c>
       <c r="L11" s="1">
-        <v>10.199155707398919</v>
+        <v>10.94768880270148</v>
       </c>
       <c r="M11" s="1">
-        <v>1162160</v>
+        <v>1162161</v>
       </c>
       <c r="N11" s="1">
-        <v>7.787123539245651</v>
+        <v>8.3587854410652813</v>
       </c>
       <c r="O11" s="1">
-        <v>4.2174820899963379</v>
+        <v>3.5986061096191406</v>
       </c>
       <c r="P11" s="1">
-        <v>41.251165804182612</v>
+        <v>37.805888399196682</v>
       </c>
       <c r="Q11" s="1">
-        <v>10.530678212868519</v>
+        <v>11.250412764300121</v>
       </c>
       <c r="R11" s="1">
-        <v>3.9172372817993164</v>
+        <v>3.3604001998901367</v>
       </c>
     </row>
     <row r="12">
@@ -739,52 +739,52 @@
         <v>3092</v>
       </c>
       <c r="C12" s="1">
-        <v>5.3064575418380189</v>
+        <v>3.9876371509776369</v>
       </c>
       <c r="D12" s="1">
         <v>30917</v>
       </c>
       <c r="E12" s="1">
-        <v>14.17732458381743</v>
+        <v>11.91454854675793</v>
       </c>
       <c r="F12" s="1">
-        <v>309161</v>
+        <v>309295</v>
       </c>
       <c r="G12" s="1">
-        <v>42.23893703455601</v>
+        <v>39.196606873817537</v>
       </c>
       <c r="H12" s="1">
-        <v>1237902</v>
+        <v>1236951</v>
       </c>
       <c r="I12" s="1">
-        <v>42.148625100592938</v>
+        <v>44.236558090447851</v>
       </c>
       <c r="J12" s="1">
-        <v>1546562</v>
+        <v>1545804</v>
       </c>
       <c r="K12" s="1">
-        <v>15.654072313085489</v>
+        <v>16.595000260348119</v>
       </c>
       <c r="L12" s="1">
-        <v>9.8935521679307303</v>
+        <v>10.500245569232289</v>
       </c>
       <c r="M12" s="1">
         <v>1082063</v>
       </c>
       <c r="N12" s="1">
-        <v>7.4175290702964576</v>
+        <v>7.8714242538396801</v>
       </c>
       <c r="O12" s="1">
-        <v>4.2693400382995605</v>
+        <v>3.7329227924346924</v>
       </c>
       <c r="P12" s="1">
-        <v>40.892699632960273</v>
+        <v>37.974041799239608</v>
       </c>
       <c r="Q12" s="1">
-        <v>10.13523550380412</v>
+        <v>10.72028018670974</v>
       </c>
       <c r="R12" s="1">
-        <v>4.0347065925598145</v>
+        <v>3.542262077331543</v>
       </c>
     </row>
     <row r="13">
@@ -795,52 +795,52 @@
         <v>3120</v>
       </c>
       <c r="C13" s="1">
-        <v>6.4329721909181421</v>
+        <v>5.2706789687595217</v>
       </c>
       <c r="D13" s="1">
-        <v>31200</v>
+        <v>31199</v>
       </c>
       <c r="E13" s="1">
-        <v>16.309525809866049</v>
+        <v>14.36384576682171</v>
       </c>
       <c r="F13" s="1">
         <v>311987</v>
       </c>
       <c r="G13" s="1">
-        <v>44.487395281928777</v>
+        <v>41.720522977877579</v>
       </c>
       <c r="H13" s="1">
         <v>1247946</v>
       </c>
       <c r="I13" s="1">
-        <v>40.491500764713102</v>
+        <v>42.336391005842451</v>
       </c>
       <c r="J13" s="1">
-        <v>1559933</v>
+        <v>1559932</v>
       </c>
       <c r="K13" s="1">
-        <v>15.02120253227371</v>
+        <v>15.943166833514329</v>
       </c>
       <c r="L13" s="1">
-        <v>9.575384101368261</v>
+        <v>10.16566329405676</v>
       </c>
       <c r="M13" s="1">
-        <v>1091953</v>
+        <v>1091954</v>
       </c>
       <c r="N13" s="1">
-        <v>7.2623164906740456</v>
+        <v>7.710026427885194</v>
       </c>
       <c r="O13" s="1">
-        <v>4.6460165977478027</v>
+        <v>4.1040630340576172</v>
       </c>
       <c r="P13" s="1">
-        <v>43.113567545190968</v>
+        <v>40.45517139448372</v>
       </c>
       <c r="Q13" s="1">
-        <v>9.8275671121916606</v>
+        <v>10.400763686191491</v>
       </c>
       <c r="R13" s="1">
-        <v>4.3870029449462891</v>
+        <v>3.8896346092224121</v>
       </c>
     </row>
     <row r="14">
@@ -851,52 +851,52 @@
         <v>3406</v>
       </c>
       <c r="C14" s="1">
-        <v>6.6952854795974606</v>
+        <v>5.2432156030627786</v>
       </c>
       <c r="D14" s="1">
         <v>34057</v>
       </c>
       <c r="E14" s="1">
-        <v>16.497366504506381</v>
+        <v>14.398880932405371</v>
       </c>
       <c r="F14" s="1">
         <v>340563</v>
       </c>
       <c r="G14" s="1">
-        <v>44.642410331708788</v>
+        <v>41.85032371105649</v>
       </c>
       <c r="H14" s="1">
-        <v>1362253</v>
+        <v>1362254</v>
       </c>
       <c r="I14" s="1">
-        <v>40.7199698143787</v>
+        <v>42.602011940805163</v>
       </c>
       <c r="J14" s="1">
-        <v>1702815</v>
+        <v>1702817</v>
       </c>
       <c r="K14" s="1">
-        <v>14.637692667575919</v>
+        <v>15.547832154884951</v>
       </c>
       <c r="L14" s="1">
-        <v>9.1156385866511211</v>
+        <v>9.6846517120213243</v>
       </c>
       <c r="M14" s="1">
-        <v>1197089</v>
+        <v>1203294</v>
       </c>
       <c r="N14" s="1">
-        <v>6.8170045720063213</v>
+        <v>7.3282131667737174</v>
       </c>
       <c r="O14" s="1">
-        <v>4.8973431587219238</v>
+        <v>4.3213038444519043</v>
       </c>
       <c r="P14" s="1">
-        <v>42.753652965493281</v>
+        <v>40.072180520405396</v>
       </c>
       <c r="Q14" s="1">
-        <v>9.4685485210965368</v>
+        <v>10.020888791684801</v>
       </c>
       <c r="R14" s="1">
-        <v>4.5153331756591797</v>
+        <v>3.9988648891448975</v>
       </c>
     </row>
     <row r="15">
@@ -907,52 +907,52 @@
         <v>3613</v>
       </c>
       <c r="C15" s="1">
-        <v>5.8145436635712624</v>
+        <v>4.8368297699316036</v>
       </c>
       <c r="D15" s="1">
         <v>36122</v>
       </c>
       <c r="E15" s="1">
-        <v>15.684312386106649</v>
+        <v>14.01219796383419</v>
       </c>
       <c r="F15" s="1">
         <v>361216</v>
       </c>
       <c r="G15" s="1">
-        <v>43.632572391531227</v>
+        <v>41.012801216699877</v>
       </c>
       <c r="H15" s="1">
-        <v>1444863</v>
+        <v>1445946</v>
       </c>
       <c r="I15" s="1">
-        <v>41.121594825244053</v>
+        <v>42.871375706505752</v>
       </c>
       <c r="J15" s="1">
-        <v>1806077</v>
+        <v>1811309</v>
       </c>
       <c r="K15" s="1">
-        <v>15.24591869209439</v>
+        <v>16.230104334406431</v>
       </c>
       <c r="L15" s="1">
-        <v>9.7251460808730279</v>
+        <v>10.20427006017351</v>
       </c>
       <c r="M15" s="1">
-        <v>1264255</v>
+        <v>1264265</v>
       </c>
       <c r="N15" s="1">
-        <v>7.1881095817011422</v>
+        <v>7.6044704405391048</v>
       </c>
       <c r="O15" s="1">
-        <v>4.486572265625</v>
+        <v>4.0191802978515625</v>
       </c>
       <c r="P15" s="1">
-        <v>41.853659300243322</v>
+        <v>39.347140442453991</v>
       </c>
       <c r="Q15" s="1">
-        <v>10.074546080808499</v>
+        <v>10.53110767441</v>
       </c>
       <c r="R15" s="1">
-        <v>4.1543965339660645</v>
+        <v>3.7362775802612305</v>
       </c>
     </row>
     <row r="16">
@@ -963,52 +963,52 @@
         <v>3613</v>
       </c>
       <c r="C16" s="1">
-        <v>7.6780021897982209</v>
+        <v>6.390497465010343</v>
       </c>
       <c r="D16" s="1">
         <v>36125</v>
       </c>
       <c r="E16" s="1">
-        <v>16.698889059772839</v>
+        <v>14.89840927560396</v>
       </c>
       <c r="F16" s="1">
-        <v>361243</v>
+        <v>361245</v>
       </c>
       <c r="G16" s="1">
-        <v>42.747854285729737</v>
+        <v>40.631573492064327</v>
       </c>
       <c r="H16" s="1">
-        <v>1444970</v>
+        <v>1444969</v>
       </c>
       <c r="I16" s="1">
-        <v>41.524283605133377</v>
+        <v>42.9786868683317</v>
       </c>
       <c r="J16" s="1">
         <v>1806211</v>
       </c>
       <c r="K16" s="1">
-        <v>15.7279475926687</v>
+        <v>16.389912340851321</v>
       </c>
       <c r="L16" s="1">
-        <v>9.8969314088634501</v>
+        <v>10.314029161171691</v>
       </c>
       <c r="M16" s="1">
         <v>1264348</v>
       </c>
       <c r="N16" s="1">
-        <v>7.3176225609718726</v>
+        <v>7.623642712090108</v>
       </c>
       <c r="O16" s="1">
-        <v>4.3193039894104004</v>
+        <v>3.9394471645355225</v>
       </c>
       <c r="P16" s="1">
-        <v>41.089719048062122</v>
+        <v>39.084533681392053</v>
       </c>
       <c r="Q16" s="1">
-        <v>10.213034055735269</v>
+        <v>10.615921493563789</v>
       </c>
       <c r="R16" s="1">
-        <v>4.0232625007629395</v>
+        <v>3.6816902160644531</v>
       </c>
     </row>
   </sheetData>
